--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-22.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-22.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
   <si>
     <t>Date: 2024-07-22</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Secured Securities Limited</t>
+    <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Investment Management Nepal Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
+    <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Linch Stock Market Limited</t>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>36</t>
+    <t>45</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>45</t>
+    <t>49</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>3,935,609,174.8</t>
-  </si>
-  <si>
-    <t>2,555,180,791.9</t>
-  </si>
-  <si>
-    <t>1,646,341,966.49</t>
-  </si>
-  <si>
-    <t>1,612,196,608.5</t>
-  </si>
-  <si>
-    <t>1,483,766,729.0</t>
-  </si>
-  <si>
-    <t>1,319,764,502.7</t>
-  </si>
-  <si>
-    <t>1,028,902,544.7</t>
-  </si>
-  <si>
-    <t>1,055,958,949.8</t>
-  </si>
-  <si>
-    <t>2,244,416,812.4</t>
-  </si>
-  <si>
-    <t>802,750,775.95</t>
-  </si>
-  <si>
-    <t>433,299,431.6</t>
-  </si>
-  <si>
-    <t>555,983,137.79</t>
-  </si>
-  <si>
-    <t>974,804,134.2</t>
-  </si>
-  <si>
-    <t>173,535,340.9</t>
-  </si>
-  <si>
-    <t>2,879,650,225.0</t>
-  </si>
-  <si>
-    <t>310,763,979.5</t>
-  </si>
-  <si>
-    <t>843,591,190.54</t>
-  </si>
-  <si>
-    <t>1,178,897,176.9</t>
-  </si>
-  <si>
-    <t>927,783,591.2</t>
-  </si>
-  <si>
-    <t>344,960,368.5</t>
-  </si>
-  <si>
-    <t>855,367,203.8</t>
+    <t>42</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>1,554,547,208.27</t>
+  </si>
+  <si>
+    <t>1,227,346,109.0</t>
+  </si>
+  <si>
+    <t>1,194,710,640.73</t>
+  </si>
+  <si>
+    <t>1,077,287,535.34</t>
+  </si>
+  <si>
+    <t>961,744,042.32</t>
+  </si>
+  <si>
+    <t>933,560,524.34</t>
+  </si>
+  <si>
+    <t>857,942,448.5</t>
+  </si>
+  <si>
+    <t>884,845,216.07</t>
+  </si>
+  <si>
+    <t>599,379,752.7</t>
+  </si>
+  <si>
+    <t>566,675,463.92</t>
+  </si>
+  <si>
+    <t>560,072,054.79</t>
+  </si>
+  <si>
+    <t>470,757,918.0</t>
+  </si>
+  <si>
+    <t>470,865,768.9</t>
+  </si>
+  <si>
+    <t>453,057,400.4</t>
+  </si>
+  <si>
+    <t>669,701,992.2</t>
+  </si>
+  <si>
+    <t>627,966,356.29</t>
+  </si>
+  <si>
+    <t>628,035,176.79</t>
+  </si>
+  <si>
+    <t>517,215,480.55</t>
+  </si>
+  <si>
+    <t>490,986,124.32</t>
+  </si>
+  <si>
+    <t>462,694,755.45</t>
+  </si>
+  <si>
+    <t>404,885,048.1</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,355 +179,337 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>169,710,187.69</t>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>62,639,342.7</t>
+  </si>
+  <si>
+    <t>CHCL</t>
+  </si>
+  <si>
+    <t>48,202,456.9</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>43,157,521.5</t>
+  </si>
+  <si>
+    <t>TAMOR</t>
+  </si>
+  <si>
+    <t>39,106,866.7</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>29,592,197.2</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>53,803,038.1</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>18,127,945.5</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>16,273,053.5</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>16,052,085.1</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>13,214,425.4</t>
   </si>
   <si>
     <t>AHPC</t>
   </si>
   <si>
-    <t>101,608,478.1</t>
-  </si>
-  <si>
-    <t>RHGCL</t>
-  </si>
-  <si>
-    <t>91,940,709.4</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>81,997,605.8</t>
+    <t>20,747,657.3</t>
+  </si>
+  <si>
+    <t>17,379,857.1</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>15,645,817.1</t>
+  </si>
+  <si>
+    <t>SMJC</t>
+  </si>
+  <si>
+    <t>14,714,231.0</t>
+  </si>
+  <si>
+    <t>14,648,812.4</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>87,469,565.6</t>
+  </si>
+  <si>
+    <t>RNLI</t>
+  </si>
+  <si>
+    <t>24,529,624.3</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>17,604,197.0</t>
+  </si>
+  <si>
+    <t>16,881,590.0</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>15,335,294.9</t>
+  </si>
+  <si>
+    <t>41,932,629.5</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>36,059,387.7</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>31,460,321.5</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>28,583,777.1</t>
+  </si>
+  <si>
+    <t>SALICO</t>
+  </si>
+  <si>
+    <t>16,695,710.6</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>37,221,342.6</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>18,514,730.8</t>
+  </si>
+  <si>
+    <t>13,246,042.7</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>13,093,153.7</t>
+  </si>
+  <si>
+    <t>12,208,977.9</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>16,590,531.9</t>
+  </si>
+  <si>
+    <t>16,256,587.9</t>
+  </si>
+  <si>
+    <t>10,551,539.6</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>10,546,579.5</t>
+  </si>
+  <si>
+    <t>10,401,787.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>21,848,377.8</t>
+  </si>
+  <si>
+    <t>21,779,402.3</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>19,298,008.7</t>
+  </si>
+  <si>
+    <t>18,393,449.89</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>15,802,391.6</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>32,150,486.1</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>16,292,715.2</t>
   </si>
   <si>
     <t>UMRH</t>
   </si>
   <si>
-    <t>81,097,710.0</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>2,088,981,774.0</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>48,917,400.0</t>
-  </si>
-  <si>
-    <t>SIKLES</t>
-  </si>
-  <si>
-    <t>19,568,356.0</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>15,385,670.2</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>8,324,643.0</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>508,564,325.0</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>36,690,670.2</t>
-  </si>
-  <si>
-    <t>IHL</t>
-  </si>
-  <si>
-    <t>32,873,713.0</t>
-  </si>
-  <si>
-    <t>GVL</t>
-  </si>
-  <si>
-    <t>30,109,286.0</t>
-  </si>
-  <si>
-    <t>NICL</t>
-  </si>
-  <si>
-    <t>16,139,840.0</t>
-  </si>
-  <si>
-    <t>216,106,250.0</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>96,317,890.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>46,567,660.0</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>32,348,264.2</t>
-  </si>
-  <si>
-    <t>SALICO</t>
-  </si>
-  <si>
-    <t>9,563,871.9</t>
-  </si>
-  <si>
-    <t>142,619,092.0</t>
-  </si>
-  <si>
-    <t>79,590,085.0</t>
-  </si>
-  <si>
-    <t>WNLB</t>
-  </si>
-  <si>
-    <t>40,182,480.0</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>27,144,332.5</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>25,558,787.5</t>
-  </si>
-  <si>
-    <t>800,504,672.0</t>
-  </si>
-  <si>
-    <t>25,354,241.2</t>
-  </si>
-  <si>
-    <t>SJCL</t>
-  </si>
-  <si>
-    <t>24,416,114.3</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>13,191,944.7</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>9,167,381.1</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>40,652,564.79</t>
-  </si>
-  <si>
-    <t>22,215,716.4</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>19,318,312.8</t>
-  </si>
-  <si>
-    <t>15,545,062.0</t>
+    <t>15,539,725.8</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>15,272,839.1</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>14,646,695.3</t>
+  </si>
+  <si>
+    <t>20,564,956.8</t>
+  </si>
+  <si>
+    <t>14,531,740.4</t>
+  </si>
+  <si>
+    <t>14,530,314.0</t>
+  </si>
+  <si>
+    <t>UMHL</t>
+  </si>
+  <si>
+    <t>14,202,819.2</t>
+  </si>
+  <si>
+    <t>14,083,931.6</t>
+  </si>
+  <si>
+    <t>24,265,971.4</t>
+  </si>
+  <si>
+    <t>HBL</t>
+  </si>
+  <si>
+    <t>15,768,914.0</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>15,690,456.8</t>
+  </si>
+  <si>
+    <t>13,474,039.5</t>
+  </si>
+  <si>
+    <t>13,397,543.8</t>
+  </si>
+  <si>
+    <t>42,153,741.6</t>
+  </si>
+  <si>
+    <t>24,335,569.1</t>
+  </si>
+  <si>
+    <t>20,572,659.6</t>
+  </si>
+  <si>
+    <t>SGHC</t>
+  </si>
+  <si>
+    <t>18,767,797.5</t>
+  </si>
+  <si>
+    <t>18,108,556.39</t>
+  </si>
+  <si>
+    <t>22,944,693.7</t>
+  </si>
+  <si>
+    <t>15,046,547.6</t>
+  </si>
+  <si>
+    <t>12,687,449.5</t>
+  </si>
+  <si>
+    <t>9,124,931.3</t>
   </si>
   <si>
     <t>NTC</t>
   </si>
   <si>
-    <t>7,968,450.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>2,118,395,650.0</t>
-  </si>
-  <si>
-    <t>305,553,701.6</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>98,576,829.2</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>75,836,492.7</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>39,970,597.0</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>121,306,142.0</t>
-  </si>
-  <si>
-    <t>74,904,750.0</t>
-  </si>
-  <si>
-    <t>17,120,305.8</t>
-  </si>
-  <si>
-    <t>7,784,864.3</t>
-  </si>
-  <si>
-    <t>MKHC</t>
-  </si>
-  <si>
-    <t>5,174,298.0</t>
-  </si>
-  <si>
-    <t>282,253,170.0</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>247,066,126.6</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>48,795,996.0</t>
-  </si>
-  <si>
-    <t>45,630,969.0</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>10,826,771.6</t>
-  </si>
-  <si>
-    <t>748,930,799.9</t>
-  </si>
-  <si>
-    <t>NWCL</t>
-  </si>
-  <si>
-    <t>196,408,550.0</t>
-  </si>
-  <si>
-    <t>113,562,182.9</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>37,275,358.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>9,660,908.9</t>
-  </si>
-  <si>
-    <t>460,064,294.0</t>
-  </si>
-  <si>
-    <t>165,791,308.3</t>
-  </si>
-  <si>
-    <t>44,636,139.3</t>
-  </si>
-  <si>
-    <t>VLUCL</t>
-  </si>
-  <si>
-    <t>22,688,386.0</t>
+    <t>9,062,216.5</t>
+  </si>
+  <si>
+    <t>11,390,567.9</t>
+  </si>
+  <si>
+    <t>10,328,422.4</t>
+  </si>
+  <si>
+    <t>9,041,469.69</t>
+  </si>
+  <si>
+    <t>8,554,396.3</t>
   </si>
   <si>
     <t>SHINE</t>
   </si>
   <si>
-    <t>14,905,574.7</t>
-  </si>
-  <si>
-    <t>105,322,957.5</t>
-  </si>
-  <si>
-    <t>86,020,512.7</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>23,266,126.0</t>
-  </si>
-  <si>
-    <t>15,880,380.4</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>6,738,013.9</t>
-  </si>
-  <si>
-    <t>759,497,521.8</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>13,516,685.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>6,640,695.0</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>5,648,589.5</t>
-  </si>
-  <si>
-    <t>5,517,442.8</t>
+    <t>7,876,808.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -545,109 +527,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>2,145,662,626.7</t>
-  </si>
-  <si>
-    <t>1,038,186,484.3</t>
-  </si>
-  <si>
-    <t>924,180,735.8</t>
-  </si>
-  <si>
-    <t>780,323,846.1</t>
-  </si>
-  <si>
-    <t>605,746,639.79</t>
+    <t>369,348,741.0</t>
+  </si>
+  <si>
+    <t>347,897,680.5</t>
+  </si>
+  <si>
+    <t>281,844,173.89</t>
+  </si>
+  <si>
+    <t>256,322,383.4</t>
+  </si>
+  <si>
+    <t>249,941,644.3</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>4,569,600,060.89</t>
+    <t>3,871,313,653.32</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>4,169,442,394.2</t>
+    <t>3,482,070,068.95</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>1,336,633,170.3</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>986,498,623.7</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>966,512,235.1</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>2,472,089,606.9</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>1,218,467,320.3</t>
+    <t>872,427,174.4</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>697,497,750.3</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>709,195,318.0</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>646,541,091.7</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>455,995,388.3</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>324,421,719.89</t>
+    <t>616,076,781.29</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>285,372,690.5</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>284,771,144.89</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>236,016,803.7</t>
+    <t>218,697,359.1</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>204,271,434.0</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>144,018,401.6</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>120,409,952.9</t>
+    <t>190,248,277.9</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>47,971,018.6</t>
+    <t>61,283,869.2</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>30,148,767.41</t>
+    <t>40,928,792.01</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>958,860.0</t>
+    <t>5,203,850.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -659,214 +641,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>528,069,805.7</t>
-  </si>
-  <si>
-    <t>179,295,647.2</t>
-  </si>
-  <si>
-    <t>87,962,820.9</t>
-  </si>
-  <si>
-    <t>83,745,030.59</t>
-  </si>
-  <si>
-    <t>35,297,465.9</t>
-  </si>
-  <si>
-    <t>2,091,714,106.5</t>
-  </si>
-  <si>
-    <t>106,315,519.1</t>
-  </si>
-  <si>
-    <t>16,609,058.9</t>
-  </si>
-  <si>
-    <t>14,268,674.3</t>
-  </si>
-  <si>
-    <t>8,543,710.8</t>
-  </si>
-  <si>
-    <t>615,599,370.29</t>
-  </si>
-  <si>
-    <t>91,764,875.9</t>
-  </si>
-  <si>
-    <t>27,141,421.1</t>
-  </si>
-  <si>
-    <t>15,662,401.6</t>
-  </si>
-  <si>
-    <t>13,348,111.6</t>
-  </si>
-  <si>
-    <t>218,082,174.0</t>
-  </si>
-  <si>
-    <t>110,050,965.6</t>
-  </si>
-  <si>
-    <t>98,029,517.3</t>
-  </si>
-  <si>
-    <t>2,275,158.0</t>
-  </si>
-  <si>
-    <t>1,711,791.0</t>
-  </si>
-  <si>
-    <t>201,626,559.3</t>
-  </si>
-  <si>
-    <t>103,343,645.7</t>
-  </si>
-  <si>
-    <t>92,579,521.8</t>
-  </si>
-  <si>
-    <t>52,370,243.6</t>
-  </si>
-  <si>
-    <t>27,610,493.5</t>
-  </si>
-  <si>
-    <t>875,518,730.1</t>
-  </si>
-  <si>
-    <t>24,182,593.8</t>
-  </si>
-  <si>
-    <t>20,346,908.89</t>
-  </si>
-  <si>
-    <t>18,029,894.2</t>
-  </si>
-  <si>
-    <t>13,598,664.7</t>
-  </si>
-  <si>
-    <t>68,281,669.8</t>
-  </si>
-  <si>
-    <t>34,558,716.7</t>
-  </si>
-  <si>
-    <t>32,681,424.3</t>
-  </si>
-  <si>
-    <t>11,036,677.8</t>
-  </si>
-  <si>
-    <t>8,460,348.0</t>
-  </si>
-  <si>
-    <t>2,131,807,372.3</t>
-  </si>
-  <si>
-    <t>361,094,035.9</t>
-  </si>
-  <si>
-    <t>181,962,770.5</t>
-  </si>
-  <si>
-    <t>76,794,332.7</t>
-  </si>
-  <si>
-    <t>54,237,725.1</t>
-  </si>
-  <si>
-    <t>174,595,422.1</t>
-  </si>
-  <si>
-    <t>94,669,868.6</t>
-  </si>
-  <si>
-    <t>11,337,112.9</t>
-  </si>
-  <si>
-    <t>10,082,629.3</t>
-  </si>
-  <si>
-    <t>9,619,652.69</t>
-  </si>
-  <si>
-    <t>330,009,234.2</t>
-  </si>
-  <si>
-    <t>282,284,670.0</t>
-  </si>
-  <si>
-    <t>147,500,557.8</t>
-  </si>
-  <si>
-    <t>15,409,671.5</t>
-  </si>
-  <si>
-    <t>14,765,448.3</t>
-  </si>
-  <si>
-    <t>967,040,951.8</t>
-  </si>
-  <si>
-    <t>114,274,000.9</t>
-  </si>
-  <si>
-    <t>37,284,628.0</t>
-  </si>
-  <si>
-    <t>24,292,410.0</t>
-  </si>
-  <si>
-    <t>13,229,267.7</t>
-  </si>
-  <si>
-    <t>537,203,498.9</t>
-  </si>
-  <si>
-    <t>166,994,865.3</t>
-  </si>
-  <si>
-    <t>77,109,403.09</t>
-  </si>
-  <si>
-    <t>46,269,663.3</t>
-  </si>
-  <si>
-    <t>22,696,240.3</t>
-  </si>
-  <si>
-    <t>173,523,349.2</t>
-  </si>
-  <si>
-    <t>105,613,809.7</t>
-  </si>
-  <si>
-    <t>22,493,889.5</t>
-  </si>
-  <si>
-    <t>14,341,794.9</t>
-  </si>
-  <si>
-    <t>8,623,534.8</t>
-  </si>
-  <si>
-    <t>773,850,378.7</t>
-  </si>
-  <si>
-    <t>25,978,456.1</t>
-  </si>
-  <si>
-    <t>22,739,078.7</t>
-  </si>
-  <si>
-    <t>16,805,058.8</t>
-  </si>
-  <si>
-    <t>3,778,613.8</t>
+    <t>311,272,690.0</t>
+  </si>
+  <si>
+    <t>204,225,125.0</t>
+  </si>
+  <si>
+    <t>90,601,757.3</t>
+  </si>
+  <si>
+    <t>64,832,990.4</t>
+  </si>
+  <si>
+    <t>49,056,550.8</t>
+  </si>
+  <si>
+    <t>212,949,192.6</t>
+  </si>
+  <si>
+    <t>122,900,469.7</t>
+  </si>
+  <si>
+    <t>51,499,426.0</t>
+  </si>
+  <si>
+    <t>46,443,707.2</t>
+  </si>
+  <si>
+    <t>41,155,026.0</t>
+  </si>
+  <si>
+    <t>156,812,341.9</t>
+  </si>
+  <si>
+    <t>142,892,863.1</t>
+  </si>
+  <si>
+    <t>61,693,264.8</t>
+  </si>
+  <si>
+    <t>38,398,733.4</t>
+  </si>
+  <si>
+    <t>34,401,610.29</t>
+  </si>
+  <si>
+    <t>217,237,832.6</t>
+  </si>
+  <si>
+    <t>141,315,562.6</t>
+  </si>
+  <si>
+    <t>41,027,667.29</t>
+  </si>
+  <si>
+    <t>30,919,016.8</t>
+  </si>
+  <si>
+    <t>27,903,834.8</t>
+  </si>
+  <si>
+    <t>157,192,733.19</t>
+  </si>
+  <si>
+    <t>85,140,411.3</t>
+  </si>
+  <si>
+    <t>85,077,733.09</t>
+  </si>
+  <si>
+    <t>43,844,395.5</t>
+  </si>
+  <si>
+    <t>25,917,409.2</t>
+  </si>
+  <si>
+    <t>114,155,066.0</t>
+  </si>
+  <si>
+    <t>112,285,881.7</t>
+  </si>
+  <si>
+    <t>76,950,789.9</t>
+  </si>
+  <si>
+    <t>49,451,989.4</t>
+  </si>
+  <si>
+    <t>25,642,211.7</t>
+  </si>
+  <si>
+    <t>112,390,173.9</t>
+  </si>
+  <si>
+    <t>110,817,202.1</t>
+  </si>
+  <si>
+    <t>60,606,248.0</t>
+  </si>
+  <si>
+    <t>39,501,138.4</t>
+  </si>
+  <si>
+    <t>34,678,784.9</t>
+  </si>
+  <si>
+    <t>184,763,145.2</t>
+  </si>
+  <si>
+    <t>151,304,609.19</t>
+  </si>
+  <si>
+    <t>64,368,882.2</t>
+  </si>
+  <si>
+    <t>60,678,127.0</t>
+  </si>
+  <si>
+    <t>53,886,647.7</t>
+  </si>
+  <si>
+    <t>190,408,736.4</t>
+  </si>
+  <si>
+    <t>157,448,978.4</t>
+  </si>
+  <si>
+    <t>55,001,585.0</t>
+  </si>
+  <si>
+    <t>49,977,730.1</t>
+  </si>
+  <si>
+    <t>41,672,385.1</t>
+  </si>
+  <si>
+    <t>174,130,498.1</t>
+  </si>
+  <si>
+    <t>155,142,307.0</t>
+  </si>
+  <si>
+    <t>67,238,961.5</t>
+  </si>
+  <si>
+    <t>42,064,220.1</t>
+  </si>
+  <si>
+    <t>41,717,973.5</t>
+  </si>
+  <si>
+    <t>138,442,789.8</t>
+  </si>
+  <si>
+    <t>137,179,088.6</t>
+  </si>
+  <si>
+    <t>85,991,142.8</t>
+  </si>
+  <si>
+    <t>28,147,346.6</t>
+  </si>
+  <si>
+    <t>27,603,679.4</t>
+  </si>
+  <si>
+    <t>173,755,587.32</t>
+  </si>
+  <si>
+    <t>69,834,244.59</t>
+  </si>
+  <si>
+    <t>65,809,104.1</t>
+  </si>
+  <si>
+    <t>58,386,279.9</t>
+  </si>
+  <si>
+    <t>35,672,863.0</t>
+  </si>
+  <si>
+    <t>140,483,164.9</t>
+  </si>
+  <si>
+    <t>114,114,346.8</t>
+  </si>
+  <si>
+    <t>53,477,635.3</t>
+  </si>
+  <si>
+    <t>27,918,342.3</t>
+  </si>
+  <si>
+    <t>27,493,442.2</t>
+  </si>
+  <si>
+    <t>110,863,338.9</t>
+  </si>
+  <si>
+    <t>107,668,098.3</t>
+  </si>
+  <si>
+    <t>29,472,247.1</t>
+  </si>
+  <si>
+    <t>29,206,306.1</t>
+  </si>
+  <si>
+    <t>28,467,152.8</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1657,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.04312170750761204</v>
+        <v>0.04029426856049556</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1684,7 +1666,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.8175475413020226</v>
+        <v>0.04383689140778464</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>74</v>
@@ -1693,43 +1675,43 @@
         <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3089056437553243</v>
+        <v>0.01736626141315912</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1340446003053355</v>
+        <v>0.08119426126246046</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.09611961854416268</v>
+        <v>0.04360061269404548</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="R9" s="15" t="s">
         <v>101</v>
       </c>
       <c r="S9" s="16">
-        <v>0.6065511463312674</v>
+        <v>0.03987030474099759</v>
       </c>
       <c r="T9" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="U9" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="U9" s="17" t="s">
-        <v>110</v>
-      </c>
       <c r="V9" s="18">
-        <v>0.03951060769497191</v>
+        <v>0.01933758135992265</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1741,7 +1723,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02581772569049963</v>
+        <v>0.03100739343493003</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1750,52 +1732,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.01914439876625154</v>
+        <v>0.01477003541793931</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.02228617805219682</v>
+        <v>0.01454733598872146</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="M10" s="16">
-        <v>0.05974326548770928</v>
+        <v>0.02276980239266443</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.0536405645472591</v>
+        <v>0.03749374689445906</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01921118589576383</v>
+        <v>0.01983238399341173</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02159166241199014</v>
+        <v>0.01894834313003456</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1807,7 +1789,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02336123972591162</v>
+        <v>0.02776211701414231</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1816,52 +1798,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.007658305847489257</v>
+        <v>0.01325873230107743</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.0199677306836117</v>
+        <v>0.01309590503893059</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.02888460362370251</v>
+        <v>0.01634122406724085</v>
       </c>
       <c r="N11" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.02708139980135651</v>
+        <v>0.03271174045862427</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="R11" s="15" t="s">
         <v>104</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01850035688188994</v>
+        <v>0.01418873480026662</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01877564877209308</v>
+        <v>0.01229865665051075</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1873,7 +1855,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02083479384209103</v>
+        <v>0.02515643557941263</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1882,34 +1864,34 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.006021362656127127</v>
+        <v>0.0130786947400507</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="J12" s="14">
-        <v>0.01828859775967017</v>
+        <v>0.01231614626869751</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.0200647142100721</v>
+        <v>0.01567045885712893</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>98</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.01829420485677975</v>
+        <v>0.02972077376330589</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>105</v>
@@ -1918,16 +1900,16 @@
         <v>106</v>
       </c>
       <c r="S12" s="16">
-        <v>0.009995680799878812</v>
+        <v>0.01402496502207634</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01510839105226678</v>
+        <v>0.01229287526038526</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1939,7 +1921,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02060613907480313</v>
+        <v>0.01903589485258032</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>72</v>
@@ -1948,52 +1930,52 @@
         <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.003257946766972172</v>
+        <v>0.01076666581911981</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.009803455374711808</v>
+        <v>0.01226138941145547</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M13" s="16">
-        <v>0.00593219949079182</v>
+        <v>0.01423509916971026</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>100</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.01722561033379257</v>
+        <v>0.0173598274232354</v>
       </c>
       <c r="Q13" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="R13" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="R13" s="15" t="s">
-        <v>108</v>
-      </c>
       <c r="S13" s="16">
-        <v>0.006946224937286305</v>
+        <v>0.01307786435003838</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.007744611033422396</v>
+        <v>0.01212410811259679</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2004,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2013,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2022,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2031,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2040,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2049,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2058,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2067,339 +2049,339 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10">
-        <v>0.5382637238382931</v>
+        <v>0.01405449617983251</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G16" s="12">
-        <v>0.04747458277102901</v>
+        <v>0.02619512610521504</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1714426138342106</v>
+        <v>0.01721333693607539</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M16" s="16">
-        <v>0.4645406124485095</v>
+        <v>0.02252506466819578</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P16" s="18">
-        <v>0.3100651099718789</v>
+        <v>0.04383052012291461</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="S16" s="16">
-        <v>0.07980435697772462</v>
+        <v>0.02457761773504236</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="V16" s="18">
-        <v>0.7381627402053407</v>
+        <v>0.0132766107096285</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10">
-        <v>0.07763822270678787</v>
+        <v>0.01401012602520931</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G17" s="12">
-        <v>0.02931485327279005</v>
+        <v>0.01327475198766447</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>135</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1500697495592272</v>
+        <v>0.01216339748269147</v>
       </c>
       <c r="K17" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="L17" s="15" t="s">
-        <v>143</v>
-      </c>
       <c r="M17" s="16">
-        <v>0.1218266735982902</v>
+        <v>0.01463760925710223</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1117367744266222</v>
+        <v>0.02530358185666083</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06517868341209175</v>
+        <v>0.01611737772489501</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="V17" s="18">
-        <v>0.0131369924874091</v>
+        <v>0.01203859584994063</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>121</v>
-      </c>
       <c r="D18" s="10">
-        <v>0.02504741320128909</v>
+        <v>0.0124139097206807</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>129</v>
       </c>
       <c r="G18" s="12">
-        <v>0.006700232662311757</v>
+        <v>0.01266124175246805</v>
       </c>
       <c r="H18" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>137</v>
-      </c>
       <c r="J18" s="14">
-        <v>0.02963904036537016</v>
+        <v>0.01216220355342411</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>144</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07043941309717748</v>
+        <v>0.01456478078984023</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03008298975006872</v>
+        <v>0.02139099250396488</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01762899816778047</v>
+        <v>0.01359038773499314</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="V18" s="18">
-        <v>0.006454153538842929</v>
+        <v>0.010538550360584</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01926931494762913</v>
+        <v>0.0118320304472898</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" s="12">
-        <v>0.003046698035879987</v>
+        <v>0.01244379151732822</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02771658010837517</v>
+        <v>0.01188808295146823</v>
       </c>
       <c r="K19" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="L19" s="15" t="s">
-        <v>146</v>
-      </c>
       <c r="M19" s="16">
-        <v>0.02312085126806046</v>
+        <v>0.01250737529012848</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01529107342586868</v>
+        <v>0.01951433715640883</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01203273793734534</v>
+        <v>0.009774332849338631</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="V19" s="18">
-        <v>0.005489916930516462</v>
+        <v>0.009970827664438613</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01015613980573445</v>
+        <v>0.01016526967848465</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G20" s="12">
-        <v>0.002025022267075066</v>
+        <v>0.01193363077667931</v>
       </c>
       <c r="H20" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>140</v>
-      </c>
       <c r="J20" s="14">
-        <v>0.006576259258629401</v>
+        <v>0.011788571324178</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M20" s="16">
-        <v>0.005992388799892455</v>
+        <v>0.01243636759952604</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01004576690437436</v>
+        <v>0.01882887296740307</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S20" s="16">
-        <v>0.00510546683610238</v>
+        <v>0.009707154773183723</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="V20" s="18">
-        <v>0.00536245422700236</v>
+        <v>0.009181044735310121</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2407,226 +2389,226 @@
         <v>64</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3283811880815551</v>
+        <v>0.278200840329818</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2996250063020476</v>
+        <v>0.250228967740301</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1776496217040933</v>
+        <v>0.09605330502509703</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D34" s="22">
-        <v>0.08756165549416974</v>
+        <v>0.07089189114454413</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05096428527726526</v>
+        <v>0.06945562671298357</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04646181919784378</v>
+        <v>0.06269447396402587</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03276879932030029</v>
+        <v>0.05012367316071301</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02331363541675926</v>
+        <v>0.04427258900047132</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01696066994338944</v>
+        <v>0.02050748903700846</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01467938009761658</v>
+        <v>0.02046426068962999</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01034946892347949</v>
+        <v>0.01571605778502464</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D42" s="22">
-        <v>0.008652915542538416</v>
+        <v>0.01367164624795794</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D43" s="22">
-        <v>0.003447299516677574</v>
+        <v>0.004403989301017087</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D44" s="22">
-        <v>0.002166554606387232</v>
+        <v>0.00294123012251964</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D45" s="22">
-        <v>6.890572080871883E-05</v>
+        <v>0.0003739597388883169</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3005,331 +2987,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D9" s="10">
-        <v>0.134177399799063</v>
+        <v>0.2002336682630592</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G9" s="12">
-        <v>0.8186168717026977</v>
+        <v>0.1735037827051929</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3739195032563358</v>
+        <v>0.1312554994941566</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1352702101283449</v>
+        <v>0.2016526001383852</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1358883140855223</v>
+        <v>0.1634454972248192</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="S9" s="16">
-        <v>0.6633901186983334</v>
+        <v>0.1222792342033544</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="V9" s="18">
-        <v>0.0663635930844248</v>
+        <v>0.1309996656494844</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04555727950530337</v>
+        <v>0.1313727392217795</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04160782651349892</v>
+        <v>0.100135136127278</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="J10" s="14">
-        <v>0.05573864832932775</v>
+        <v>0.1196045789068127</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="M10" s="16">
-        <v>0.06826150422335416</v>
+        <v>0.1311772001094285</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="P10" s="18">
-        <v>0.06964952352695597</v>
+        <v>0.08852710030271374</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0183234158446653</v>
+        <v>0.120277024114939</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03358793976943306</v>
+        <v>0.129166242203949</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02235049696073292</v>
+        <v>0.05828176643205802</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G11" s="12">
-        <v>0.006500150186104723</v>
+        <v>0.04195998636599743</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01648589518608062</v>
+        <v>0.05163866688447988</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="M11" s="16">
-        <v>0.06080493953600821</v>
+        <v>0.03808423095387484</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06239493040957653</v>
+        <v>0.08846192890861931</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01541707543912107</v>
+        <v>0.08242721054810849</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="V11" s="18">
-        <v>0.03176338173945232</v>
+        <v>0.07064139104663965</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02127879748228704</v>
+        <v>0.04170538537208549</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>183</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G12" s="12">
-        <v>0.005584213197450501</v>
+        <v>0.0378407580872528</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="J12" s="14">
-        <v>0.009513455842586718</v>
+        <v>0.03214061387830056</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="M12" s="16">
-        <v>0.001411216217677585</v>
+        <v>0.02870080251133206</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03529546968295715</v>
+        <v>0.0455884243319406</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01366144805616009</v>
+        <v>0.05297138011960328</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01072665030993581</v>
+        <v>0.04604171115330937</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D13" s="10">
-        <v>0.008968742660224575</v>
+        <v>0.03155680994377345</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G13" s="12">
-        <v>0.003343681522295338</v>
+        <v>0.03353171994290324</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="J13" s="14">
-        <v>0.008107739383245003</v>
+        <v>0.02879493086207025</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>185</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="M13" s="16">
-        <v>0.001061775586783217</v>
+        <v>0.02590193786186742</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01860837890509135</v>
+        <v>0.02694834390393502</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01030385699280408</v>
+        <v>0.02746711223447845</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="V13" s="18">
-        <v>0.00822269129722758</v>
+        <v>0.04042087550351578</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3340,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3349,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3358,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3367,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3376,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3385,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3394,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3403,331 +3385,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D16" s="10">
-        <v>0.5416715119860279</v>
+        <v>0.1188533511347116</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="G16" s="12">
-        <v>0.06832996813903451</v>
+        <v>0.1551385831622822</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2004499921140803</v>
+        <v>0.1457511904251574</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="M16" s="16">
-        <v>0.5998281764776457</v>
+        <v>0.1285105278369543</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="P16" s="18">
-        <v>0.3620538784166254</v>
+        <v>0.1806671834439984</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="S16" s="16">
-        <v>0.13148053978191</v>
+        <v>0.1504810467407164</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="V16" s="18">
-        <v>0.7521124159777774</v>
+        <v>0.1292200183052255</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D17" s="10">
-        <v>0.09175048127545593</v>
+        <v>0.09733034056159766</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03705016447372582</v>
+        <v>0.1282840897489658</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1714617471616973</v>
+        <v>0.129857642269934</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="M17" s="16">
-        <v>0.0708809336885539</v>
+        <v>0.1273374879951915</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1125479241690154</v>
+        <v>0.07261208962785977</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="S17" s="16">
-        <v>0.08002473887116467</v>
+        <v>0.1222356171062965</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="V17" s="18">
-        <v>0.02524870429548273</v>
+        <v>0.1254957118490215</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.0414068365743835</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.04623496958618788</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>193</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G18" s="12">
-        <v>0.004436912227870133</v>
+        <v>0.04481342678864516</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08959290402738812</v>
+        <v>0.05628054125216061</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0231266011871157</v>
+        <v>0.07982190453179461</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05196868321206304</v>
+        <v>0.06842683833138154</v>
       </c>
       <c r="Q18" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.05728352249816292</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="R18" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.01704386612458629</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>191</v>
-      </c>
       <c r="U18" s="17" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02210032312305156</v>
+        <v>0.03435224256770179</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01951269277237177</v>
+        <v>0.03903266924104963</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.04072016013536733</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.003945955343732326</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>187</v>
-      </c>
       <c r="I19" s="13" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J19" s="14">
-        <v>0.009359945754680243</v>
+        <v>0.03520870967910493</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>181</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01506789548614784</v>
+        <v>0.02612797946358417</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="P19" s="18">
-        <v>0.03118392021849952</v>
+        <v>0.06070875132135542</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01086693487410767</v>
+        <v>0.02990523010753738</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01633299371895314</v>
+        <v>0.03404226723023602</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01378127824462048</v>
+        <v>0.03466388631579</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G20" s="12">
-        <v>0.003764764016109775</v>
+        <v>0.03395324659802217</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J20" s="14">
-        <v>0.008968639930548528</v>
+        <v>0.0349188933937252</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="M20" s="16">
-        <v>0.008205740931503764</v>
+        <v>0.0256233164259455</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01529636691294215</v>
+        <v>0.03709184713424054</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="S20" s="16">
-        <v>0.006534146646888748</v>
+        <v>0.02945009078992769</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="V20" s="18">
-        <v>0.003672470069652458</v>
+        <v>0.03318072540852954</v>
       </c>
     </row>
   </sheetData>
